--- a/new-stats/fc-kryvbas-kryvyi-rih.xlsx
+++ b/new-stats/fc-kryvbas-kryvyi-rih.xlsx
@@ -827,22 +827,58 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kryvbas</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LNZ Cherkasy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
